--- a/giro_da_praça_ofertas - TERÇA.xlsx
+++ b/giro_da_praça_ofertas - TERÇA.xlsx
@@ -1,153 +1,75 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{369D3E1A-D4B5-4600-98C7-1E9C5B32FAB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
+    <sheet name="Ofertas Finais" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
-  <si>
-    <t>NOME_PROMOÇÃO</t>
-  </si>
-  <si>
-    <t>SESSÃO</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>PRODUTO</t>
-  </si>
-  <si>
-    <t>TIPO</t>
-  </si>
-  <si>
-    <t>PROMOÇÃO</t>
-  </si>
-  <si>
-    <t>TERÇA - AÇOUGUE 23/12/25</t>
-  </si>
-  <si>
-    <t>#06 AÇOUGUE - #02 BOVINA</t>
-  </si>
-  <si>
-    <t>BISTECA BOVINA DA PALETA KG</t>
-  </si>
-  <si>
-    <t>BISTECA BOVINA DO ACÉM KG</t>
-  </si>
-  <si>
-    <t>CAPA DO CONTRA FILE KG</t>
-  </si>
-  <si>
-    <t>CARNE MOIDA KG</t>
-  </si>
-  <si>
-    <t>CONTRA FILÉ KG</t>
-  </si>
-  <si>
-    <t>COXÃO MOLE KG</t>
-  </si>
-  <si>
-    <t>MIOLO DO ACEM KG BOVINO</t>
-  </si>
-  <si>
-    <t>#06 AÇOUGUE - #03 SUÍNA</t>
-  </si>
-  <si>
-    <t>BISTECA SUINA CARRE KG</t>
-  </si>
-  <si>
-    <t>BISTECA SUINA DO PERNIL KG</t>
-  </si>
-  <si>
-    <t>SUAN SUINA KG</t>
-  </si>
-  <si>
-    <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
-  </si>
-  <si>
-    <t>LINGUIÇA CASEIRA BOVINA KG</t>
-  </si>
-  <si>
-    <t>LINGUIÇA SUINA FINA APIMENTADA FRICÓ KG</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
     <font>
-      <sz val="7"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="7"/>
     </font>
     <font>
-      <i/>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -160,62 +82,108 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -503,259 +471,643 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="31" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="3">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>NOME_PROMOÇÃO</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>SESSÃO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>PRODUTO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TIPO</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>PROMOÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA/TERÇA - PERECIVEIS 22 E 23/12/25</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - CONGELADOS - BATATAS</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>230387</v>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>BATATAS CONGELADAS BOUA PCT 1,05KG PRE-FRITAS</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr"/>
+      <c r="F2" s="6" t="n">
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA/TERÇA - PERECIVEIS 22 E 23/12/25</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - CONGELADOS - BATATAS</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>193650</v>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>BATATAS CONGELADAS BOUA PCT 400G PRE-FRITAS</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr"/>
+      <c r="F3" s="6" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA/TERÇA - PERECIVEIS 22 E 23/12/25</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - CONGELADOS - MASSAS</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>127336</v>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PIZZA CONGELADA SEARA 440G MUSSARELA </t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="6" t="n">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA/TERÇA - PERECIVEIS 22 E 23/12/25</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>268844</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>MARGARINA DELICIA 500G COM CREME DE LEITE</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="6" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA/TERÇA - PERECIVEIS 22 E 23/12/25</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - LATICÍNIOS - BEBIDAS LACTEAS</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>322738</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>IOGURTE ACTIVIA 800G</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>MORANGO, VITAMINA DE FRUTAS</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>16.99</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA/TERÇA - PERECIVEIS 22 E 23/12/25</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #01 AVES</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>289785</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>COXA DE FRANGO SEARA PCT 1KG</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="6" t="n">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA/TERÇA - PERECIVEIS 22 E 23/12/25</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #01 AVES</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>289794</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>MEIO DA ASA DE FRANGO SEARA 1KG</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="6" t="n">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 23/12/25</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>105460</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="7">
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>BISTECA BOVINA DA PALETA KG</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="6" t="n">
         <v>23.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="3">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 23/12/25</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>158997</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="7">
-        <v>16.989999999999998</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="3">
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>BISTECA BOVINA DO ACÉM KG</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="6" t="n">
+        <v>16.99</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 23/12/25</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>239334</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="7">
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>CAPA DO CONTRA FILE KG</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="6" t="n">
         <v>28.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="3">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 23/12/25</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>105468</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="7">
-        <v>18.989999999999998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="3">
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>CARNE MOIDA KG</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="6" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 23/12/25</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>105451</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="7">
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>CONTRA FILÉ KG</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="6" t="n">
         <v>38.99</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="3">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 23/12/25</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>105435</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="7">
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>COXÃO MOLE KG</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="6" t="n">
         <v>38.99</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="3">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 23/12/25</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>231292</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="7">
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>MIOLO DO ACEM KG BOVINO</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="6" t="n">
         <v>26.99</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="3">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 23/12/25</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #03 SUÍNA</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>106053</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="7">
-        <v>18.989999999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="3">
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>BISTECA SUINA CARRE KG</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="6" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 23/12/25</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #03 SUÍNA</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>105062</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="7">
-        <v>18.989999999999998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="3">
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>BISTECA SUINA DO PERNIL KG</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="6" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 23/12/25</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #03 SUÍNA</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>106034</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="7">
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>SUAN SUINA KG</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="6" t="n">
         <v>10.99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="3">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA/TERÇA - PERECIVEIS 22 E 23/12/25</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>295493</v>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>ISCAS DE FRANGO EMPANADAS SEARA 300G APIMENTADAS</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="6" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA/TERÇA - PERECIVEIS 22 E 23/12/25</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>293660</v>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>ISCAS DE FRANGO EMPANADAS SEARA 300G TRADICIONAL</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="6" t="n">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA/TERÇA - PERECIVEIS 22 E 23/12/25</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>194424</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>LINGUIÇA CALABRESA BOUA 400G</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="6" t="n">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 23/12/25</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>305039</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="7">
-        <v>18.989999999999998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="3">
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>LINGUIÇA CASEIRA BOVINA KG</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="6" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA/TERÇA - PERECIVEIS 22 E 23/12/25</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>227259</v>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LINGUIÇA DEFUMADA SEARA 215G FININHA </t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="6" t="n">
+        <v>7.49</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 23/12/25</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>167154</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="7">
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>LINGUIÇA SUINA FINA APIMENTADA FRICÓ KG</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="6" t="n">
         <v>25.99</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA/TERÇA - PERECIVEIS 22 E 23/12/25</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>301962</v>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>LINGUIÇA SUÍNA BONFRIGO KG</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="6" t="n">
+        <v>16.99</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - TERÇA.xlsx
+++ b/giro_da_praça_ofertas - TERÇA.xlsx
@@ -476,14 +476,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="53" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -522,241 +522,225 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 06/01/2026</t>
+          <t>SEGUNDA - PERECIVEIS 05/01/2025</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
+          <t>#02 MERCEARIA - CONGELADOS - BATATAS</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>105460</v>
+        <v>193650</v>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>BISTECA BOVINA DA PALETA KG</t>
+          <t>BATATAS CONGELADAS BOUA PCT 400G PRE-FRITAS</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr"/>
       <c r="F2" s="6" t="n">
-        <v>23.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 06/01/2026</t>
+          <t>SEGUNDA - PERECIVEIS 05/01/2025</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
+          <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>105457</v>
+        <v>268844</v>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>CARNE BOVINA SERENADA KG</t>
+          <t>MARGARINA DELICIA 500G COM CREME DE LEITE</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr"/>
       <c r="F3" s="6" t="n">
-        <v>34.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 06/01/2026</t>
+          <t>SEGUNDA - PERECIVEIS 05/01/2025</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
+          <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>105468</v>
+        <v>142662</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>CARNE MOIDA KG</t>
+          <t xml:space="preserve">MARGARINA QUALY 250G AREADA </t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="6" t="n">
-        <v>18.99</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 06/01/2026</t>
+          <t>SEGUNDA - PERECIVEIS 05/01/2025</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
+          <t>#02 MERCEARIA - LATICÍNIOS - QUEIJO</t>
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>105449</v>
+        <v>302944</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>COXÃO DURO KG</t>
+          <t>REQUEIJÃO DE FRUTAP 175G MISTURA DE AMIDO</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr"/>
       <c r="F5" s="6" t="n">
-        <v>34.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TERÇA - AÇOUGUE 06/01/2026</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>231292</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>MIOLO DO ACEM KG BOVINO</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="6" t="n">
-        <v>27.99</v>
-      </c>
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 06/01/2026</t>
+          <t>SEGUNDA - PERECIVEIS 05/01/2025</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #02 BOVINA</t>
+          <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>105475</v>
+        <v>119923</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>MUSCULO BOVINO KG</t>
+          <t>CORAÇÃO DE FRANGO AMERICANO 1KG</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr"/>
       <c r="F7" s="6" t="n">
-        <v>19.99</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 06/01/2026</t>
+          <t>SEGUNDA - PERECIVEIS 05/01/2025</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #03 SUÍNA</t>
+          <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>106008</v>
+        <v>111565</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>INGREDIENTES PARA FEIJOADA KG</t>
+          <t>COXA DE FRANGO SADIA BDJ 1KG</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr"/>
       <c r="F8" s="6" t="n">
-        <v>16.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 06/01/2026</t>
+          <t>SEGUNDA - PERECIVEIS 05/01/2025</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #03 SUÍNA</t>
+          <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
       <c r="C9" s="3" t="n">
-        <v>258810</v>
+        <v>108785</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>PANCETA SUINA KG</t>
+          <t>COXINHA DA ASA DE FRANGO SADIA PCT 1KG DRUMETE</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr"/>
       <c r="F9" s="6" t="n">
-        <v>16.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 06/01/2026</t>
+          <t>SEGUNDA - PERECIVEIS 05/01/2025</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #03 SUÍNA</t>
+          <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>106034</v>
+        <v>195365</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>SUAN SUINA KG</t>
+          <t>MOELA DE FRANGO PERDIGÃO BDJ 1KG</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr"/>
       <c r="F10" s="6" t="n">
-        <v>10.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 06/01/2026</t>
+          <t>SEGUNDA - PERECIVEIS 05/01/2025</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #03 SUÍNA</t>
+          <t>#06 AÇOUGUE - #01 AVES</t>
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>106032</v>
+        <v>108771</v>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>TOUCINHO FRESCO KG</t>
+          <t>SOBRECOXA DE FRANGO SADIA BDJ 1KG</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr"/>
       <c r="F11" s="6" t="n">
-        <v>18.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="12">
@@ -767,20 +751,360 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>305039</v>
+        <v>105460</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>LINGUIÇA CASEIRA BOVINA KG</t>
+          <t>BISTECA BOVINA DA PALETA KG</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr"/>
       <c r="F12" s="6" t="n">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 06/01/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>105457</v>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>CARNE BOVINA SERENADA KG</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="6" t="n">
+        <v>34.99</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 06/01/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>105468</v>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>CARNE MOIDA KG</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="6" t="n">
         <v>18.99</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 06/01/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>105449</v>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>COXÃO DURO KG</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="6" t="n">
+        <v>34.99</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 06/01/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>231292</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>MIOLO DO ACEM KG BOVINO</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="6" t="n">
+        <v>27.99</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 06/01/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>105475</v>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>MUSCULO BOVINO KG</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="6" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 06/01/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #03 SUÍNA</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>106008</v>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>INGREDIENTES PARA FEIJOADA KG</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="6" t="n">
+        <v>16.99</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 06/01/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #03 SUÍNA</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>258810</v>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>PANCETA SUINA KG</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="6" t="n">
+        <v>16.99</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 06/01/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #03 SUÍNA</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>106034</v>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>SUAN SUINA KG</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="6" t="n">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 06/01/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #03 SUÍNA</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>106032</v>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>TOUCINHO FRESCO KG</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="6" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA - PERECIVEIS 05/01/2025</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>105713</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>LINGUICA TIPO CALABRESA SADIA KG</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="6" t="n">
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 06/01/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>305039</v>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>LINGUIÇA CASEIRA BOVINA KG</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="6" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA - PERECIVEIS 05/01/2025</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>167157</v>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>LINGUIÇA DE FRANGO FRICO KG FINA COM CHEIRO VERDE</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="6" t="n">
+        <v>27.99</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA - PERECIVEIS 05/01/2025</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>170464</v>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>STEAK EMPANADO SADIA 100G FRANGO</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="6" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA - PERECIVEIS 05/01/2025</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>138538</v>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>TEKITOS SEARA 300G</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>FRANGO, QUEIJO COM OREGANO</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>8.99</v>
       </c>
     </row>
   </sheetData>

--- a/giro_da_praça_ofertas - TERÇA.xlsx
+++ b/giro_da_praça_ofertas - TERÇA.xlsx
@@ -1,150 +1,75 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCB44C84-B4C8-4DF7-9495-2A7C7B2E3480}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
+    <sheet name="Ofertas Finais" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="21">
-  <si>
-    <t>NOME_PROMOÇÃO</t>
-  </si>
-  <si>
-    <t>SESSÃO</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>PRODUTO</t>
-  </si>
-  <si>
-    <t>TIPO</t>
-  </si>
-  <si>
-    <t>PROMOÇÃO</t>
-  </si>
-  <si>
-    <t>TERÇA - AÇOUGUE 13/01/2026</t>
-  </si>
-  <si>
-    <t>#06 AÇOUGUE - #01 AVES</t>
-  </si>
-  <si>
-    <t>FRANGO MARINGA KG CONGELADO</t>
-  </si>
-  <si>
-    <t>#06 AÇOUGUE - #02 BOVINA</t>
-  </si>
-  <si>
-    <t>ACEM BOVINO KG</t>
-  </si>
-  <si>
-    <t>BISTECA BOVINA DA MAÇÃ DO PEITO KG</t>
-  </si>
-  <si>
-    <t>BISTECA BOVINA DO CONTRA FILE KG</t>
-  </si>
-  <si>
-    <t>CARNE BOVINA SERENADA KG</t>
-  </si>
-  <si>
-    <t>CARNE MOIDA KG</t>
-  </si>
-  <si>
-    <t>CONTRA FILÉ KG</t>
-  </si>
-  <si>
-    <t>COSTELA BOVINA KG</t>
-  </si>
-  <si>
-    <t>#06 AÇOUGUE - #03 SUÍNA</t>
-  </si>
-  <si>
-    <t>BISTECA SUINA CARRE KG</t>
-  </si>
-  <si>
-    <t>INGREDIENTES PARA FEIJOADA KG</t>
-  </si>
-  <si>
-    <t>PANCETA SUINA KG</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
     <font>
-      <sz val="7"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <color rgb="00000000"/>
+      <sz val="7"/>
     </font>
     <font>
-      <i/>
+      <name val="Calibri"/>
+      <color rgb="00000000"/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -157,62 +82,108 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -500,241 +471,667 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="53" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="3">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>NOME_PROMOÇÃO</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>SESSÃO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>PRODUTO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TIPO</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>PROMOÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA - PERECIVEIS 12 e 13/01/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - CONGELADOS - BATATAS</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>120994</v>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>BATATAS CONGELADAS BEM BRASIL 400G PALITO</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr"/>
+      <c r="F2" s="6" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA - PERECIVEIS 12 e 13/01/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - CONGELADOS - MASSAS</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>272599</v>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>PIZZA SADIA 460G 4 QUEIJOS</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr"/>
+      <c r="F3" s="6" t="n">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA - PERECIVEIS 12 e 13/01/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>268844</v>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>MARGARINA DELICIA 500G COM CREME DE LEITE</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="6" t="n">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA - PERECIVEIS 12 e 13/01/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>#02 MERCEARIA - LATICÍNIOS - QUEIJO</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>155246</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>REQUEIJÃO CANTO DE MINAS 200G CREMOSO TRADICIONAL</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="6" t="n">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA - PERECIVEIS 12 e 13/01/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #01 AVES</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>119923</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>CORAÇÃO DE FRANGO AMERICANO 1KG</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="6" t="n">
+        <v>27.99</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA - PERECIVEIS 12 e 13/01/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #01 AVES</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>111565</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>COXA DE FRANGO SADIA BDJ 1KG</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="6" t="n">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA - PERECIVEIS 12 e 13/01/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #01 AVES</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>108785</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>COXINHA DA ASA DE FRANGO SADIA PCT 1KG DRUMETE</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="6" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 13/01/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #01 AVES</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>105853</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="7">
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>FRANGO MARINGA KG CONGELADO</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="6" t="n">
         <v>10.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="3">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA - PERECIVEIS 12 e 13/01/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #01 AVES</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>195365</v>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>MOELA DE FRANGO PERDIGÃO BDJ 1KG</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="6" t="n">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA - PERECIVEIS 12 e 13/01/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #01 AVES</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>108771</v>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>SOBRECOXA DE FRANGO SADIA BDJ 1KG</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="6" t="n">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 13/01/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>105470</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="7">
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>ACEM BOVINO KG</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="6" t="n">
         <v>23.99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="3">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 13/01/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>105459</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="7">
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>BISTECA BOVINA DA MAÇÃ DO PEITO KG</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="6" t="n">
         <v>23.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="3">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 13/01/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>105461</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="7">
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>BISTECA BOVINA DO CONTRA FILE KG</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="6" t="n">
         <v>33.99</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="3">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 13/01/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>105457</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="7">
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>CARNE BOVINA SERENADA KG</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="6" t="n">
         <v>34.99</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="3">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 13/01/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>105468</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="7">
-        <v>19.989999999999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="3">
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>CARNE MOIDA KG</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="6" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 13/01/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>105451</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="7">
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>CONTRA FILÉ KG</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="6" t="n">
         <v>38.99</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="3">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 13/01/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #02 BOVINA</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>105471</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="7">
-        <v>19.989999999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="3">
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>COSTELA BOVINA KG</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="6" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 13/01/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #03 SUÍNA</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>106053</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="7">
-        <v>18.989999999999998</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="3">
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>BISTECA SUINA CARRE KG</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="6" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 13/01/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #03 SUÍNA</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>106008</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="7">
-        <v>18.989999999999998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="3">
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>INGREDIENTES PARA FEIJOADA KG</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="6" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 13/01/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #03 SUÍNA</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>258810</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="7">
-        <v>18.989999999999998</v>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>PANCETA SUINA KG</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="6" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA - PERECIVEIS 12 e 13/01/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>105713</v>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>LINGUICA TIPO CALABRESA SADIA KG</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="6" t="n">
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA - PERECIVEIS 12 e 13/01/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>272499</v>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>LINGUIÇA SUINA FARIAS KG</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="6" t="n">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA - PERECIVEIS 12 e 13/01/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>292399</v>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>LINGUIÇA SUPER FRANGO 400G DEFUMADA</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="6" t="n">
+        <v>11.49</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA - PERECIVEIS 12 e 13/01/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>170464</v>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>STEAK EMPANADO SADIA 100G FRANGO</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="6" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>SEGUNDA - PERECIVEIS 12 e 13/01/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>#06 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>138538</v>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>TEKITOS SEARA 300G</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>FRANGO, QUEIJO COM OREGANO</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>8.59</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;LGIRO DA PRAÇA - TERÇA&amp;C&amp;P - &amp;N</oddHeader>
-  </headerFooter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - TERÇA.xlsx
+++ b/giro_da_praça_ofertas - TERÇA.xlsx
@@ -1,31 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE0FEA1-F086-4F55-93BB-650F8C305D71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0D0C8D-F907-4275-89E6-F1601F232528}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="37">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -52,12 +47,6 @@
   </si>
   <si>
     <t>BATATAS CONGELADAS PALITO SADIA 400G PRE FRITA</t>
-  </si>
-  <si>
-    <t>#02 MERCEARIA - CONGELADOS - CARNES</t>
-  </si>
-  <si>
-    <t>FEIJOADA NA PANELINHA SEARA 300G CONGELADA</t>
   </si>
   <si>
     <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
@@ -149,7 +138,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="\R\$\ #,##0.00"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -229,7 +218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -246,13 +235,9 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -555,18 +540,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="41.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44" customWidth="1"/>
+    <col min="2" max="2" width="48" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -585,7 +567,7 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
@@ -603,7 +585,7 @@
         <v>8</v>
       </c>
       <c r="E2" s="5"/>
-      <c r="F2" s="7">
+      <c r="F2" s="6">
         <v>11.99</v>
       </c>
     </row>
@@ -615,14 +597,14 @@
         <v>9</v>
       </c>
       <c r="C3" s="3">
-        <v>319483</v>
+        <v>276943</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="5"/>
-      <c r="F3" s="7">
-        <v>3.49</v>
+      <c r="F3" s="6">
+        <v>15.99</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -633,284 +615,284 @@
         <v>11</v>
       </c>
       <c r="C4" s="3">
-        <v>276943</v>
+        <v>302944</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E4" s="5"/>
-      <c r="F4" s="7">
-        <v>15.99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="F4" s="6">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3">
-        <v>302944</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="C6" s="3">
+        <v>119923</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="7">
-        <v>5.99</v>
+      <c r="E6" s="5"/>
+      <c r="F6" s="6">
+        <v>28.99</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3">
-        <v>119923</v>
+        <v>105853</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E7" s="5"/>
-      <c r="F7" s="7">
-        <v>28.99</v>
+      <c r="F7" s="6">
+        <v>9.99</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="3">
+        <v>247629</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="3">
-        <v>105853</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>18</v>
-      </c>
       <c r="E8" s="5"/>
-      <c r="F8" s="7">
-        <v>9.99</v>
+      <c r="F8" s="6">
+        <v>17.989999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C9" s="3">
-        <v>247629</v>
+        <v>105459</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E9" s="5"/>
-      <c r="F9" s="7">
-        <v>17.989999999999998</v>
+      <c r="F9" s="6">
+        <v>22.99</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="3">
+        <v>105461</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="3">
-        <v>105459</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>22</v>
-      </c>
       <c r="E10" s="5"/>
-      <c r="F10" s="7">
-        <v>22.99</v>
+      <c r="F10" s="6">
+        <v>33.99</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C11" s="3">
-        <v>105461</v>
+        <v>105457</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E11" s="5"/>
-      <c r="F11" s="7">
-        <v>33.99</v>
+      <c r="F11" s="6">
+        <v>34.99</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C12" s="3">
-        <v>105457</v>
+        <v>322584</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E12" s="5"/>
-      <c r="F12" s="7">
-        <v>34.99</v>
+      <c r="F12" s="6">
+        <v>39.99</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C13" s="3">
-        <v>322584</v>
+        <v>105458</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E13" s="5"/>
-      <c r="F13" s="7">
-        <v>39.99</v>
+      <c r="F13" s="6">
+        <v>17.989999999999998</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C14" s="3">
-        <v>105458</v>
+        <v>105463</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E14" s="5"/>
-      <c r="F14" s="7">
-        <v>17.989999999999998</v>
+      <c r="F14" s="6">
+        <v>13.99</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C15" s="3">
-        <v>105463</v>
+        <v>105471</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" s="5"/>
-      <c r="F15" s="7">
-        <v>13.99</v>
+      <c r="F15" s="6">
+        <v>21.99</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C16" s="3">
-        <v>105471</v>
+        <v>105449</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E16" s="5"/>
-      <c r="F16" s="7">
-        <v>21.99</v>
+      <c r="F16" s="6">
+        <v>32.99</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C17" s="3">
-        <v>105449</v>
+        <v>105062</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E17" s="5"/>
-      <c r="F17" s="7">
-        <v>32.99</v>
+      <c r="F17" s="6">
+        <v>19.989999999999998</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="3">
+        <v>106008</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="3">
-        <v>105062</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>31</v>
-      </c>
       <c r="E18" s="5"/>
-      <c r="F18" s="7">
-        <v>19.989999999999998</v>
+      <c r="F18" s="6">
+        <v>18.989999999999998</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C19" s="3">
-        <v>106008</v>
+        <v>106032</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E19" s="5"/>
-      <c r="F19" s="7">
-        <v>18.989999999999998</v>
+      <c r="F19" s="6">
+        <v>19.989999999999998</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C20" s="3">
-        <v>106032</v>
+        <v>330507</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>33</v>
       </c>
       <c r="E20" s="5"/>
-      <c r="F20" s="7">
-        <v>19.989999999999998</v>
+      <c r="F20" s="6">
+        <v>8.99</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -921,41 +903,19 @@
         <v>34</v>
       </c>
       <c r="C21" s="3">
-        <v>330507</v>
+        <v>138538</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="7">
+      <c r="E21" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" s="6">
         <v>8.99</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" s="3">
-        <v>138538</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" s="7">
-        <v>8.99</v>
-      </c>
-    </row>
   </sheetData>
-  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="86" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;LGIRO DA PRAÇA - TERÇA&amp;C&amp;P - &amp;N</oddHeader>
-  </headerFooter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - TERÇA.xlsx
+++ b/giro_da_praça_ofertas - TERÇA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{045F28C2-1AF3-4D05-8559-79159B2CEF95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74AC4DB6-7726-4672-987A-ADAF13BBAFCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="34">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -40,19 +40,28 @@
     <t>PROMOÇÃO</t>
   </si>
   <si>
-    <t>SEGUNDA  E  TERÇA  DOS PERECIVEIS</t>
+    <t>SEGUNDA E TERÇA DOS PERECIVEIS</t>
+  </si>
+  <si>
+    <t>#02 MERCEARIA - CONGELADOS - BATATAS</t>
+  </si>
+  <si>
+    <t>BATATAS CONGELADAS MCCAIN 1,2KG AIRFRYER FININHAS</t>
   </si>
   <si>
     <t>#02 MERCEARIA - GORDURAS E MARGARINAS</t>
   </si>
   <si>
-    <t>MARGARINA DELICIA 1KG COM CREME DE LEITE</t>
+    <t>MARGARINA QUALY 1KG CREMOSA</t>
   </si>
   <si>
     <t>#02 MERCEARIA - LATICÍNIOS - QUEIJO</t>
   </si>
   <si>
-    <t>REQUEIJÃO DE FRUTAP 175G MISTURA DE AMIDO</t>
+    <t>QUEIJO MUSSARELA DEALE 150G FATIADO ZERO LACTOSE</t>
+  </si>
+  <si>
+    <t>REQUEIJÃO QUALY 200G CREMOSO TRADICIONAL</t>
   </si>
   <si>
     <t>#06 AÇOUGUE - #01 AVES</t>
@@ -61,40 +70,40 @@
     <t>CORAÇÃO DE PERU PERDIGÃO PCT 1KG</t>
   </si>
   <si>
-    <t>COXA COM SOBRECOXA SADIA 1KG A PASSARINHO</t>
-  </si>
-  <si>
     <t>COXINHA DA ASA DE FRANGO SADIA PCT 1KG DRUMETE</t>
   </si>
   <si>
-    <t>FILEZINHO DE PEITO DE FRANGO SADIA PCT 1KG</t>
+    <t>FILE PEITO DE FRANGO SADIA PCT 1KG</t>
+  </si>
+  <si>
+    <t>MEIO DA ASA DE FRANGO SEARA 1KG</t>
   </si>
   <si>
     <t>MOELA DE FRANGO PERDIGÃO BDJ 1KG</t>
   </si>
   <si>
-    <t>AÇOUGUE TERÇA FEIRA 30/06/26</t>
+    <t>OFERTA AÇOUGUE TERÇA 07/07</t>
   </si>
   <si>
     <t>#06 AÇOUGUE - #02 BOVINA</t>
   </si>
   <si>
-    <t>CARNE DE SOL KG SEGUNDA</t>
-  </si>
-  <si>
-    <t>CHAMBARI KG</t>
-  </si>
-  <si>
-    <t>COXÃO MOLE KG</t>
+    <t>COSTELA BOVINA KG</t>
+  </si>
+  <si>
+    <t>COXÃO DURO KG</t>
+  </si>
+  <si>
+    <t>FRALDINHA BOVINA KG</t>
+  </si>
+  <si>
+    <t>SUINO CAIPIRA KG</t>
   </si>
   <si>
     <t>#06 AÇOUGUE - #03 SUÍNA</t>
   </si>
   <si>
-    <t>BISTECA SUINA CARRE KG</t>
-  </si>
-  <si>
-    <t>TOUCINHO FRESCO KG</t>
+    <t>SUAN SUINA KG</t>
   </si>
   <si>
     <t>#06 AÇOUGUE - #06 EMBUTIDOS E FRIOS</t>
@@ -103,7 +112,7 @@
     <t>LINGUIÇA CASEIRA BOVINA KG</t>
   </si>
   <si>
-    <t>LINGUIÇA NUTRIBRAS 350G CALABRESA</t>
+    <t>LINGUIÇA SUPER FRANGO 400G DEFUMADA</t>
   </si>
   <si>
     <t>#06 AÇOUGUE - #07 EMPANADOS E PRATOS PRONTOS</t>
@@ -112,7 +121,7 @@
     <t>STEAK EMPANADO PERDIGÃO 100G FRANGO</t>
   </si>
   <si>
-    <t>TEKITOS SEARA 300G FRANGO</t>
+    <t>TEKITOS SEARA 300G QUEIJO COM OREGANO</t>
   </si>
 </sst>
 </file>
@@ -122,7 +131,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,21 +151,31 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -200,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -208,22 +227,26 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -529,328 +552,364 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultRowHeight="41.25" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.28515625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5703125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="75.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
-        <v>276943</v>
-      </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="5">
+        <v>342178</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="7">
-        <v>15.69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E2" s="7"/>
+      <c r="F2" s="8">
+        <v>36.49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3">
-        <v>302944</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="C3" s="5">
+        <v>139140</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="7">
-        <v>6.59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E3" s="7"/>
+      <c r="F3" s="8">
+        <v>21.89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="5">
+        <v>309333</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="8">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="5">
+        <v>142756</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8">
+        <v>8.89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="5">
         <v>345608</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="7">
-        <v>21.29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="3">
-        <v>111324</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="7">
-        <v>20.49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="3">
+      <c r="D7" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8">
+        <v>21.19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="5">
         <v>108785</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="7"/>
+      <c r="F8" s="8">
+        <v>18.989999999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="7">
-        <v>18.989999999999998</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="3">
-        <v>108786</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="7">
-        <v>24.19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="3">
+      <c r="C9" s="5">
+        <v>108856</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="7"/>
+      <c r="F9" s="8">
+        <v>23.89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="5">
+        <v>289794</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="7"/>
+      <c r="F10" s="8">
+        <v>29.49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="5">
         <v>195365</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="7">
+      <c r="D11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="7"/>
+      <c r="F11" s="8">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="3">
-        <v>105456</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="7">
-        <v>34.99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="3">
-        <v>105458</v>
-      </c>
-      <c r="D11" s="4" t="s">
+    <row r="12" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="7">
+      <c r="B12" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="5">
+        <v>105471</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="7"/>
+      <c r="F12" s="8">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="5">
+        <v>105449</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="7"/>
+      <c r="F13" s="8">
+        <v>37.99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="5">
+        <v>105474</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="7"/>
+      <c r="F14" s="8">
+        <v>38.99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="5">
+        <v>298422</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="7"/>
+      <c r="F15" s="8">
         <v>22.99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="3">
-        <v>105435</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="7">
-        <v>40.99</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="3">
-        <v>106053</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="7">
-        <v>18.989999999999998</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" s="3">
-        <v>106032</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="7">
-        <v>18.989999999999998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C15" s="3">
-        <v>305039</v>
-      </c>
-      <c r="D15" s="4" t="s">
+    <row r="16" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="7">
-        <v>20.99</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="3">
-        <v>330507</v>
-      </c>
-      <c r="D16" s="4" t="s">
+      <c r="C16" s="5">
+        <v>106034</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="7">
-        <v>9.19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E16" s="7"/>
+      <c r="F16" s="8">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="3">
-        <v>170266</v>
-      </c>
-      <c r="D17" s="4" t="s">
+      <c r="C17" s="5">
+        <v>305039</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="7">
-        <v>2.29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E17" s="7"/>
+      <c r="F17" s="8">
+        <v>18.989999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="3">
-        <v>138538</v>
-      </c>
-      <c r="D18" s="4" t="s">
+      <c r="C18" s="5">
+        <v>292399</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="7">
+      <c r="E18" s="7"/>
+      <c r="F18" s="8">
+        <v>10.19</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C19" s="5">
+        <v>170266</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="7"/>
+      <c r="F19" s="8">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="5">
+        <v>127328</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E20" s="7"/>
+      <c r="F20" s="8">
         <v>9.7899999999999991</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;LGIRO DA PRAÇA - TERÇA&amp;C&amp;P - &amp;N</oddHeader>
   </headerFooter>

--- a/giro_da_praça_ofertas - TERÇA.xlsx
+++ b/giro_da_praça_ofertas - TERÇA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C3E0B18-FB0A-4451-8CED-8C9E7E712982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEDA01A2-08B8-4924-9AB6-85F1BA03C0C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21480" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="59">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -121,6 +121,9 @@
     <t>FRALDINHA BOVINA KG</t>
   </si>
   <si>
+    <t>MAÇÃ DO PEITO KG</t>
+  </si>
+  <si>
     <t>PATINHO BOVINO KG</t>
   </si>
   <si>
@@ -164,6 +167,36 @@
   </si>
   <si>
     <t>FRANGO, QUEIJO COM OREGANO</t>
+  </si>
+  <si>
+    <t>TERCA DA PERFUMARIA</t>
+  </si>
+  <si>
+    <t>#07 HIGIENE PESSOAL - CABELOS</t>
+  </si>
+  <si>
+    <t>SHAMPOO PANTENE 510ML QUERATINA</t>
+  </si>
+  <si>
+    <t>SPRAY CAPILAR PANTENE 160ML MULTIBENEFICIOS QUERATINA</t>
+  </si>
+  <si>
+    <t>#07 HIGIENE PESSOAL - DESODORANTE</t>
+  </si>
+  <si>
+    <t>DESODORANTE LEITE DE ROSAS 310ML</t>
+  </si>
+  <si>
+    <t>LOÇÃO HIDRATANTE NIVEA 400ML BELEZA RADIANTE</t>
+  </si>
+  <si>
+    <t>#07 HIGIENE PESSOAL - INTIMA</t>
+  </si>
+  <si>
+    <t>BODY SPLASH SALON LINE 200ML PODER P</t>
+  </si>
+  <si>
+    <t>ÓLEO REPARADOR DOVE 110ML BOND INTENSE REPAIR SPRAY</t>
   </si>
 </sst>
 </file>
@@ -173,7 +206,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,24 +226,47 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -221,6 +277,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45A045"/>
+        <bgColor rgb="FF45A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -251,7 +313,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -259,27 +321,46 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -583,564 +664,697 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F39"/>
+  <sheetFormatPr defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="54.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="10" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.5703125" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="37.5703125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="91.85546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" style="16" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="6">
         <v>227504</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="6">
+      <c r="E2" s="15"/>
+      <c r="F2" s="8">
         <v>22.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="6">
         <v>284048</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="6">
+      <c r="E3" s="15"/>
+      <c r="F3" s="8">
         <v>9.89</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="6">
         <v>276943</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="6">
+      <c r="E4" s="15"/>
+      <c r="F4" s="8">
         <v>15.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="6">
         <v>158733</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="6">
+      <c r="E5" s="15"/>
+      <c r="F5" s="8">
         <v>11.99</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="6">
         <v>104770</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="6">
+      <c r="E6" s="15"/>
+      <c r="F6" s="8">
         <v>9.69</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="6">
         <v>133484</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="6">
+      <c r="E7" s="15"/>
+      <c r="F7" s="8">
         <v>9.49</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="6">
         <v>338924</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="6">
+      <c r="E8" s="15"/>
+      <c r="F8" s="8">
         <v>11.99</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="6">
         <v>286928</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="8">
         <v>11.99</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="6">
         <v>224719</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="6">
+      <c r="E11" s="15"/>
+      <c r="F11" s="8">
         <v>34.99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="6">
         <v>289786</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="6">
+      <c r="E12" s="15"/>
+      <c r="F12" s="8">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="6">
         <v>140899</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="6">
+      <c r="E13" s="15"/>
+      <c r="F13" s="8">
         <v>22.99</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="6">
         <v>289794</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="9"/>
-      <c r="F14" s="6">
+      <c r="E14" s="15"/>
+      <c r="F14" s="8">
         <v>29.99</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="6">
         <v>195365</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="6">
+      <c r="E15" s="15"/>
+      <c r="F15" s="8">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="6">
         <v>291441</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="6">
+      <c r="E16" s="15"/>
+      <c r="F16" s="8">
         <v>15.99</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="6">
         <v>105457</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="6">
+      <c r="E17" s="15"/>
+      <c r="F17" s="8">
         <v>37.99</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="6">
         <v>105456</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="6">
+      <c r="E18" s="15"/>
+      <c r="F18" s="8">
         <v>38.99</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="6">
         <v>105468</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="9"/>
-      <c r="F19" s="6">
+      <c r="E19" s="15"/>
+      <c r="F19" s="8">
         <v>20.99</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="6">
         <v>105474</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="9"/>
-      <c r="F20" s="6">
+      <c r="E20" s="15"/>
+      <c r="F20" s="8">
         <v>38.99</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+    <row r="21" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="3">
-        <v>105452</v>
-      </c>
-      <c r="D21" s="4" t="s">
+      <c r="C21" s="11">
+        <v>107260</v>
+      </c>
+      <c r="D21" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E21" s="9"/>
-      <c r="F21" s="6">
-        <v>39.99</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E21" s="17"/>
+      <c r="F21" s="13">
+        <v>35.99</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="6">
+        <v>105452</v>
+      </c>
+      <c r="D22" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="3">
-        <v>105062</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E22" s="9"/>
-      <c r="F22" s="6">
-        <v>19.989999999999998</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E22" s="15"/>
+      <c r="F22" s="8">
+        <v>39.99</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" s="3">
+        <v>35</v>
+      </c>
+      <c r="C23" s="6">
+        <v>105062</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="15"/>
+      <c r="F23" s="8">
+        <v>19.989999999999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C24" s="6">
         <v>106034</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" s="9"/>
-      <c r="F23" s="6">
+      <c r="D24" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="15"/>
+      <c r="F24" s="8">
         <v>11.99</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C24" s="3">
+    <row r="25" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="6">
         <v>171321</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D25" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" s="15"/>
+      <c r="F25" s="8">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E24" s="9"/>
-      <c r="F24" s="6">
-        <v>4.49</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C25" s="3">
+      <c r="C26" s="6">
         <v>343440</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E25" s="9"/>
-      <c r="F25" s="6">
+      <c r="D26" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E26" s="15"/>
+      <c r="F26" s="8">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C26" s="3">
+    <row r="27" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="6">
         <v>330578</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E26" s="9"/>
-      <c r="F26" s="6">
+      <c r="D27" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" s="15"/>
+      <c r="F27" s="8">
         <v>8.49</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C27" s="3">
+    <row r="28" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28" s="6">
         <v>292399</v>
       </c>
-      <c r="D27" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E27" s="9"/>
-      <c r="F27" s="6">
+      <c r="D28" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E28" s="15"/>
+      <c r="F28" s="8">
         <v>10.99</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C28" s="3">
+    <row r="29" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="6">
         <v>170705</v>
       </c>
-      <c r="D28" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E28" s="9"/>
-      <c r="F28" s="6">
+      <c r="D29" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" s="15"/>
+      <c r="F29" s="8">
         <v>5.69</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" s="3">
+    <row r="30" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" s="6">
         <v>345268</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D30" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="15"/>
+      <c r="F30" s="8">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E29" s="9"/>
-      <c r="F29" s="6">
-        <v>13.99</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="3">
+      <c r="C31" s="6">
         <v>326673</v>
       </c>
-      <c r="D30" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E30" s="9"/>
-      <c r="F30" s="6">
+      <c r="D31" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31" s="15"/>
+      <c r="F31" s="8">
         <v>14.99</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C31" s="3">
+    <row r="32" spans="1:6" ht="63" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="6">
         <v>138538</v>
       </c>
-      <c r="D31" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E31" s="9" t="s">
+      <c r="D32" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="F31" s="6">
+      <c r="E32" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F32" s="8">
         <v>8.69</v>
       </c>
     </row>
+    <row r="34" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" s="11">
+        <v>326164</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" s="17"/>
+      <c r="F34" s="13">
+        <v>41.99</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" s="11">
+        <v>313855</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="E35" s="17"/>
+      <c r="F35" s="13">
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" s="11">
+        <v>120019</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E36" s="17"/>
+      <c r="F36" s="13">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" s="11">
+        <v>267899</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E37" s="17"/>
+      <c r="F37" s="13">
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" s="11">
+        <v>342005</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E38" s="17"/>
+      <c r="F38" s="13">
+        <v>32.99</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C39" s="11">
+        <v>312196</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E39" s="17"/>
+      <c r="F39" s="13">
+        <v>53.99</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
+  <pageSetup paperSize="9" scale="92" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;LGIRO DA PRAÇA - TERÇA&amp;C&amp;P - &amp;N</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>